--- a/en/downloads/data-excel/17.4.1.xlsx
+++ b/en/downloads/data-excel/17.4.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B837F215-CEEA-48DF-929A-E85A8B52D2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -64,16 +65,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -102,6 +111,25 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -145,39 +173,58 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{B71B6A42-71CF-4F34-AC0A-0A9AA75D065B}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{ABA9FBBA-AF60-4259-AE2E-8B0C4C4483DA}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{104518EC-DC91-43CE-8CD1-4E658449F9B6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -193,9 +240,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -233,9 +280,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -270,7 +317,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -305,7 +352,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -478,7 +525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -546,16 +593,16 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
     </row>
     <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -591,34 +638,34 @@
       <c r="K4" s="6">
         <v>2014</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="11">
         <v>2015</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="11">
         <v>2016</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="11">
         <v>2017</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="11">
         <v>2018</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="13">
         <v>2019</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="13">
         <v>2020</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="13">
         <v>2021</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="13">
         <v>2022</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="13">
         <v>2023</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="13">
         <v>2024</v>
       </c>
     </row>
@@ -656,35 +703,35 @@
       <c r="K5" s="8">
         <v>6.8</v>
       </c>
-      <c r="L5" s="8">
-        <v>7.6</v>
-      </c>
-      <c r="M5" s="8">
-        <v>12.2</v>
-      </c>
-      <c r="N5" s="8">
-        <v>11.3</v>
-      </c>
-      <c r="O5" s="8">
-        <v>13</v>
-      </c>
-      <c r="P5" s="8">
-        <v>12.9</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>15.2</v>
-      </c>
-      <c r="R5" s="8">
-        <v>10.4</v>
-      </c>
-      <c r="S5" s="8">
-        <v>10.4</v>
-      </c>
-      <c r="T5" s="8">
-        <v>10.8</v>
-      </c>
-      <c r="U5" s="8">
+      <c r="L5" s="12">
+        <v>4</v>
+      </c>
+      <c r="M5" s="12">
+        <v>5.4</v>
+      </c>
+      <c r="N5" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="O5" s="12">
+        <v>6.2</v>
+      </c>
+      <c r="P5" s="14">
         <v>6.5</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>8</v>
+      </c>
+      <c r="R5" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="S5" s="14">
+        <v>7.1</v>
+      </c>
+      <c r="T5" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="U5" s="14">
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
